--- a/dynamic_live_backup.xlsx
+++ b/dynamic_live_backup.xlsx
@@ -448,7 +448,7 @@
         <v>Cash</v>
       </c>
       <c r="F2" t="str">
-        <v>Ilyas</v>
+        <v>No description provided</v>
       </c>
       <c r="G2" t="str">
         <v>Niyaz 29</v>

--- a/dynamic_live_backup.xlsx
+++ b/dynamic_live_backup.xlsx
@@ -432,7 +432,7 @@
         <v>30704209</v>
       </c>
       <c r="E2" t="str">
-        <v>given</v>
+        <v/>
       </c>
     </row>
     <row r="3">
